--- a/tests/antares/resources/expected_output_files/thermal/specific_2035.xlsx
+++ b/tests/antares/resources/expected_output_files/thermal/specific_2035.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,207 +417,207 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Cluster</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>node_ENTSOE</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>comments</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>cluster_PEMMDB</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>min_stable_gen</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>spinning</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>efficiency</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>FO_rate</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>FO_duration</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PO_duration</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>PO_winter</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>marginal_cost</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>market_bid</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>MR_specific</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>CM_specific</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>nb_unit</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>F5</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>F6</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>F7</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>F8</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>F9</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>F10</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>F11</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>F12</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>P12</t>
         </is>
@@ -650,7 +638,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -888,7 +876,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>0.1951219512195122</v>
+        <v>0.06057164489873178</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1007,7 +995,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>0.7959349593495936</v>
+        <v>0.5</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1245,7 +1233,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>0.9928463476070529</v>
+        <v>0.4</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1364,7 +1352,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>0.2481045751633987</v>
+        <v>0.2</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1483,7 +1471,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>0.1377410468319559</v>
+        <v>0.07864108210128971</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1721,7 +1709,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>2.759856630824373</v>
+        <v>0.6194690265486725</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1959,7 +1947,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>0.6941573033707865</v>
+        <v>0.348056338028169</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -2078,7 +2066,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>1.219512195121951</v>
+        <v>0.3175336296980544</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -2197,7 +2185,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>0.7224014393556351</v>
+        <v>0.1921209931257863</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -2212,7 +2200,7 @@
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>27.00000000000001</v>
+        <v>27</v>
       </c>
       <c r="L15" t="n">
         <v>0.15</v>
@@ -2316,7 +2304,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>2.043902439024391</v>
+        <v>0.2364559819413093</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -2435,7 +2423,7 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>4.375</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -2554,7 +2542,7 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>0.9786407766990292</v>
+        <v>0.490272373540856</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -2673,7 +2661,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>1.375</v>
+        <v>0.360655737704918</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -2792,7 +2780,7 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>1.624761904761905</v>
+        <v>0.4335451080050826</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -2911,7 +2899,7 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>0.404</v>
+        <v>0.2082474226804124</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -3030,7 +3018,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>1.684210526315789</v>
+        <v>0.3437164339419979</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -3149,7 +3137,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>0.1590909090909091</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -3268,7 +3256,7 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>2.633663366336634</v>
+        <v>0.6717171717171717</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -3280,10 +3268,10 @@
         <v>0.03512626262626262</v>
       </c>
       <c r="J24" t="n">
-        <v>1.898989898989899</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>40.48484848484848</v>
+        <v>40</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3387,7 +3375,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>2.333333333333333</v>
+        <v>0.875</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -3399,7 +3387,7 @@
         <v>0.01</v>
       </c>
       <c r="J25" t="n">
-        <v>1.3125</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>40</v>
@@ -3863,7 +3851,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>0.7213114754098361</v>
+        <v>0.3946188340807175</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -3982,7 +3970,7 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>1.536443481236455</v>
+        <v>0.5121478270788182</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -4101,7 +4089,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>2.708487084870849</v>
+        <v>0.6771217712177122</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -4339,7 +4327,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>0.8034433285509323</v>
+        <v>0.4017216642754661</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -4458,7 +4446,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>5.079754601226994</v>
+        <v>0.8466257668711656</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -4696,7 +4684,7 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
-        <v>1.353039175257732</v>
+        <v>0.3387382178953781</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -4815,7 +4803,7 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>1.028169014084507</v>
+        <v>0.365</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -4934,7 +4922,7 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
-        <v>1.438127090301003</v>
+        <v>0.4842342342342342</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -5053,7 +5041,7 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
-        <v>0.3700272728123276</v>
+        <v>0.2</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -5172,7 +5160,7 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
-        <v>1.515789473684211</v>
+        <v>0.3694955427889524</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -5187,7 +5175,7 @@
         <v>7</v>
       </c>
       <c r="K40" t="n">
-        <v>54.00000000000001</v>
+        <v>54</v>
       </c>
       <c r="L40" t="n">
         <v>0.15</v>
@@ -5291,7 +5279,7 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>0.584</v>
+        <v>0.4</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -5410,7 +5398,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
-        <v>8.885294117647058</v>
+        <v>0.3769182782283219</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -5422,7 +5410,7 @@
         <v>0.04730000000000002</v>
       </c>
       <c r="J42" t="n">
-        <v>3.670000000000001</v>
+        <v>4</v>
       </c>
       <c r="K42" t="n">
         <v>70</v>
@@ -5529,7 +5517,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>1.978171122994652</v>
+        <v>0.3199777868890746</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -5541,10 +5529,10 @@
         <v>0.04730000000000002</v>
       </c>
       <c r="J43" t="n">
-        <v>3.670000000000001</v>
+        <v>4</v>
       </c>
       <c r="K43" t="n">
-        <v>70.00000000000001</v>
+        <v>70</v>
       </c>
       <c r="L43" t="n">
         <v>0.4600000000000001</v>
@@ -5660,7 +5648,7 @@
         <v>0.0473</v>
       </c>
       <c r="J44" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="K44" t="n">
         <v>70</v>
@@ -5767,7 +5755,7 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
-        <v>2.026545454545454</v>
+        <v>0.3982136477313326</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -5779,7 +5767,7 @@
         <v>0.04730000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="K45" t="n">
         <v>70</v>
@@ -5886,7 +5874,7 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>3.426720647773279</v>
+        <v>0.3577194539537636</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -5898,10 +5886,10 @@
         <v>0.0473</v>
       </c>
       <c r="J46" t="n">
-        <v>3.670000000000001</v>
+        <v>4</v>
       </c>
       <c r="K46" t="n">
-        <v>69.99999999999999</v>
+        <v>70</v>
       </c>
       <c r="L46" t="n">
         <v>0.46</v>
@@ -6005,7 +5993,7 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>2.677549467275494</v>
+        <v>0.3992623694961416</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -6017,7 +6005,7 @@
         <v>0.04729999999999999</v>
       </c>
       <c r="J47" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="K47" t="n">
         <v>70</v>
@@ -6124,7 +6112,7 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
-        <v>2.149694693288204</v>
+        <v>0.2302244854524251</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -6136,10 +6124,10 @@
         <v>0.07181435772930708</v>
       </c>
       <c r="J48" t="n">
-        <v>1.668368956047404</v>
+        <v>2</v>
       </c>
       <c r="K48" t="n">
-        <v>37.76399442323535</v>
+        <v>38</v>
       </c>
       <c r="L48" t="n">
         <v>0.2276008900279758</v>
@@ -6243,7 +6231,7 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
-        <v>2.157096565132858</v>
+        <v>0.3642691415313225</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -6255,10 +6243,10 @@
         <v>0.0473</v>
       </c>
       <c r="J49" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="K49" t="n">
-        <v>69.99999999999999</v>
+        <v>70</v>
       </c>
       <c r="L49" t="n">
         <v>0.46</v>
@@ -6362,7 +6350,7 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="n">
-        <v>0.8564150943396227</v>
+        <v>0.2821182174156255</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -6374,7 +6362,7 @@
         <v>0.03899999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="K50" t="n">
         <v>36</v>
@@ -6481,7 +6469,7 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="n">
-        <v>1.692525252525253</v>
+        <v>0.460878335014211</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -6493,7 +6481,7 @@
         <v>0.0207</v>
       </c>
       <c r="J51" t="n">
-        <v>0.9900000000000001</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
         <v>59</v>
@@ -6600,7 +6588,7 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="n">
-        <v>0.8609271523178808</v>
+        <v>0.4304635761589404</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -6612,7 +6600,7 @@
         <v>0.0207</v>
       </c>
       <c r="J52" t="n">
-        <v>0.9900000000000001</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
         <v>59</v>
@@ -6719,7 +6707,7 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>3.88458070333634</v>
+        <v>0.390140823811752</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -6731,10 +6719,10 @@
         <v>0.04730000000000002</v>
       </c>
       <c r="J53" t="n">
-        <v>3.670000000000001</v>
+        <v>4</v>
       </c>
       <c r="K53" t="n">
-        <v>70.00000000000001</v>
+        <v>70</v>
       </c>
       <c r="L53" t="n">
         <v>0.46</v>
@@ -6838,7 +6826,7 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
-        <v>1.553625</v>
+        <v>0.3381102387908662</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -6850,7 +6838,7 @@
         <v>0.04730000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="K54" t="n">
         <v>70</v>
@@ -6957,7 +6945,7 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
-        <v>0.8436046511627907</v>
+        <v>0.1006806239789063</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -6969,7 +6957,7 @@
         <v>0.04729999999999999</v>
       </c>
       <c r="J55" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="K55" t="n">
         <v>70</v>
@@ -7314,7 +7302,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>1.216906666666667</v>
+        <v>0.3893353809401928</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -7552,7 +7540,7 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="n">
-        <v>0.2423076923076923</v>
+        <v>0.1148377688662049</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -7671,7 +7659,7 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
-        <v>0.7927272727272728</v>
+        <v>0.4</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -7790,7 +7778,7 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
-        <v>0.5887436925863631</v>
+        <v>0.4</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -7909,7 +7897,7 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="n">
-        <v>1.554434228360013</v>
+        <v>0.5990410458839226</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -8147,7 +8135,7 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
-        <v>0.9986642920747997</v>
+        <v>0.5</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -8742,7 +8730,7 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="n">
-        <v>2.067475409836066</v>
+        <v>0.3168578522602152</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -8861,7 +8849,7 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
-        <v>2.214</v>
+        <v>0.5</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -8980,7 +8968,7 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="n">
-        <v>0.7527441822931902</v>
+        <v>0.4</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -9099,7 +9087,7 @@
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
-        <v>0.8803560424512155</v>
+        <v>0.4</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -9218,7 +9206,7 @@
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="n">
-        <v>2.642884615384616</v>
+        <v>1.242242903755823</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -9337,7 +9325,7 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="n">
-        <v>0.7009840561697035</v>
+        <v>0.6763542288382415</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -9575,7 +9563,7 @@
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
-        <v>23.53484398915174</v>
+        <v>0.5</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -9694,7 +9682,7 @@
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>8.862747380675204</v>
+        <v>0.3099841854359429</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -9813,7 +9801,7 @@
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>1.270448675021525</v>
+        <v>0.6482159418167619</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -9932,7 +9920,7 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -9947,7 +9935,7 @@
         <v>2</v>
       </c>
       <c r="K80" t="n">
-        <v>97.5</v>
+        <v>98</v>
       </c>
       <c r="L80" t="n">
         <v>0.0375</v>
@@ -10170,7 +10158,7 @@
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>0.7038461538461539</v>
+        <v>0.2534626038781164</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -10185,7 +10173,7 @@
         <v>2</v>
       </c>
       <c r="K82" t="n">
-        <v>41.71745152354571</v>
+        <v>42</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -10289,7 +10277,7 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -10408,7 +10396,7 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -10527,7 +10515,7 @@
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
-        <v>0.9600000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -10542,7 +10530,7 @@
         <v>2</v>
       </c>
       <c r="K85" t="n">
-        <v>92.5</v>
+        <v>92</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -10646,7 +10634,7 @@
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>1.816</v>
+        <v>0.6355205599300088</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -10658,10 +10646,10 @@
         <v>0.030498687664042</v>
       </c>
       <c r="J86" t="n">
-        <v>3.099737532808399</v>
+        <v>3</v>
       </c>
       <c r="K86" t="n">
-        <v>23.21084864391951</v>
+        <v>23</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -10765,7 +10753,7 @@
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="n">
-        <v>0.7191489361702127</v>
+        <v>0.3755555555555555</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -10780,7 +10768,7 @@
         <v>2</v>
       </c>
       <c r="K87" t="n">
-        <v>22.35555555555555</v>
+        <v>22</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -11122,7 +11110,7 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>1.237373737373737</v>
+        <v>0.6186868686868687</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -11241,7 +11229,7 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="n">
-        <v>4.347826086956522</v>
+        <v>0.4488498223302786</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -11479,7 +11467,7 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="n">
-        <v>3.760204081632653</v>
+        <v>0.5537190082644629</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -11598,7 +11586,7 @@
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="n">
-        <v>25.20472727272728</v>
+        <v>0.6599143129165345</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -11717,7 +11705,7 @@
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="n">
-        <v>1.13265306122449</v>
+        <v>0.5080091533180778</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -11955,7 +11943,7 @@
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="n">
-        <v>1.536130536130536</v>
+        <v>0.4</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -12193,7 +12181,7 @@
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="n">
-        <v>2.484429065743945</v>
+        <v>0.439717470297636</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -12431,7 +12419,7 @@
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="n">
-        <v>0.6269854539374686</v>
+        <v>0.2089951513124896</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -12446,7 +12434,7 @@
         <v>1</v>
       </c>
       <c r="K101" t="n">
-        <v>7.000000000000001</v>
+        <v>7</v>
       </c>
       <c r="L101" t="n">
         <v>0.15</v>
@@ -12550,7 +12538,7 @@
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="n">
-        <v>1.154285714285714</v>
+        <v>0.4</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -12669,7 +12657,7 @@
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="n">
-        <v>1.013913043478261</v>
+        <v>0.4</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -12788,7 +12776,7 @@
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="n">
-        <v>0.3776041666666667</v>
+        <v>0.25</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -12907,7 +12895,7 @@
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="n">
-        <v>0.882706106870229</v>
+        <v>0.2856936380481779</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -13026,7 +13014,7 @@
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="n">
-        <v>0.6184971098265896</v>
+        <v>0.253314393939394</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -13038,10 +13026,10 @@
         <v>0.07517045454545455</v>
       </c>
       <c r="J106" t="n">
-        <v>1.482954545454545</v>
+        <v>1</v>
       </c>
       <c r="K106" t="n">
-        <v>68.48674242424242</v>
+        <v>68</v>
       </c>
       <c r="L106" t="n">
         <v>0.01363636363636364</v>
@@ -13145,7 +13133,7 @@
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="n">
-        <v>0.8667447306791569</v>
+        <v>0.4469806763285025</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -13160,7 +13148,7 @@
         <v>1</v>
       </c>
       <c r="K107" t="n">
-        <v>25.71739130434782</v>
+        <v>26</v>
       </c>
       <c r="L107" t="n">
         <v>0.5616545893719807</v>
@@ -13264,7 +13252,7 @@
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="n">
-        <v>0.05981334249585128</v>
+        <v>0.01677926423000926</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -13383,7 +13371,7 @@
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="n">
-        <v>0.05509641873278237</v>
+        <v>0.04040404040404041</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -13502,7 +13490,7 @@
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -13621,7 +13609,7 @@
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="n">
-        <v>0.9306358381502891</v>
+        <v>0.3252525252525252</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -13636,7 +13624,7 @@
         <v>1</v>
       </c>
       <c r="K111" t="n">
-        <v>6.141414141414141</v>
+        <v>6</v>
       </c>
       <c r="L111" t="n">
         <v>0.4104040404040404</v>
@@ -13740,7 +13728,7 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="n">
-        <v>1.627118644067797</v>
+        <v>0.4489127893383212</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -13755,7 +13743,7 @@
         <v>7</v>
       </c>
       <c r="K112" t="n">
-        <v>29.79658639233107</v>
+        <v>30</v>
       </c>
       <c r="L112" t="n">
         <v>0.15</v>
@@ -13859,7 +13847,7 @@
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="n">
-        <v>1.052631578947368</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -13874,7 +13862,7 @@
         <v>1</v>
       </c>
       <c r="K113" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="L113" t="n">
         <v>0.15</v>
@@ -14097,7 +14085,7 @@
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -14216,7 +14204,7 @@
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -14335,7 +14323,7 @@
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
-        <v>0.7759036144578313</v>
+        <v>0.400497512437811</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -14454,7 +14442,7 @@
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
-        <v>1.80948275862069</v>
+        <v>0.398292220113852</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -14573,7 +14561,7 @@
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -14811,7 +14799,7 @@
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
-        <v>2.839999999999999</v>
+        <v>0.4067369385884509</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -14826,7 +14814,7 @@
         <v>1</v>
       </c>
       <c r="K121" t="n">
-        <v>17.5627864344638</v>
+        <v>18</v>
       </c>
       <c r="L121" t="n">
         <v>0.15</v>
@@ -15049,7 +15037,7 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
-        <v>1.406779661016949</v>
+        <v>0.3802687843616371</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -15287,7 +15275,7 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="n">
-        <v>0.5178571428571429</v>
+        <v>0.2589285714285715</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -15406,7 +15394,7 @@
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
-        <v>1.328428927680798</v>
+        <v>0.5087870105062082</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -15525,7 +15513,7 @@
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
-        <v>0.3206342728889148</v>
+        <v>0.2946928496798564</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -15644,7 +15632,7 @@
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="n">
-        <v>0.3533333333333333</v>
+        <v>0.175448275862069</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -16001,7 +15989,7 @@
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="n">
-        <v>0.2505454545454546</v>
+        <v>0.1093650793650794</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -16120,7 +16108,7 @@
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="n">
-        <v>0.1721854304635762</v>
+        <v>0.1660280970625798</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -16239,7 +16227,7 @@
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="n">
-        <v>0.326</v>
+        <v>0.1314516129032258</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -16358,7 +16346,7 @@
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="n">
-        <v>2.522151898734177</v>
+        <v>0.4027693551647463</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -16477,7 +16465,7 @@
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="n">
-        <v>0.3300247487762296</v>
+        <v>0.2785546766443466</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -16596,7 +16584,7 @@
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="n">
-        <v>0.9100434782608694</v>
+        <v>0.3564847142978795</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -16715,7 +16703,7 @@
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="n">
-        <v>0.275</v>
+        <v>0.2291666666666667</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -16834,7 +16822,7 @@
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="n">
-        <v>0.8479864636209813</v>
+        <v>0.3305804749340369</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -16953,7 +16941,7 @@
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="n">
-        <v>2.5085</v>
+        <v>0.3365511899480516</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -16968,7 +16956,7 @@
         <v>1</v>
       </c>
       <c r="K139" t="n">
-        <v>26.52625088846592</v>
+        <v>27</v>
       </c>
       <c r="L139" t="n">
         <v>0.15</v>
@@ -17072,7 +17060,7 @@
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="n">
-        <v>0.1811015911872705</v>
+        <v>0.1759334126040428</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -17191,7 +17179,7 @@
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="n">
-        <v>0.6124999999999999</v>
+        <v>0.1529078014184397</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -17310,7 +17298,7 @@
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
-        <v>6.247601279317697</v>
+        <v>0.342394520986545</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -17325,7 +17313,7 @@
         <v>1</v>
       </c>
       <c r="K142" t="n">
-        <v>26.48140544033504</v>
+        <v>26</v>
       </c>
       <c r="L142" t="n">
         <v>0.15</v>
@@ -17429,7 +17417,7 @@
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>0.3078111540810348</v>
+        <v>0.2830948191816993</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -17444,7 +17432,7 @@
         <v>1</v>
       </c>
       <c r="K143" t="n">
-        <v>26.93753094550646</v>
+        <v>27</v>
       </c>
       <c r="L143" t="n">
         <v>0.15</v>
@@ -17548,7 +17536,7 @@
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>0.5752777777777778</v>
+        <v>0.2984149855907781</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -17563,7 +17551,7 @@
         <v>1</v>
       </c>
       <c r="K144" t="n">
-        <v>19.73775216138328</v>
+        <v>20</v>
       </c>
       <c r="L144" t="n">
         <v>0.15</v>
@@ -17786,7 +17774,7 @@
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>0.08548387096774193</v>
+        <v>0.06309523809523809</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -17801,7 +17789,7 @@
         <v>1</v>
       </c>
       <c r="K146" t="n">
-        <v>23.33333333333333</v>
+        <v>23</v>
       </c>
       <c r="L146" t="n">
         <v>0.15</v>
@@ -17905,7 +17893,7 @@
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="n">
-        <v>0.4173333333333333</v>
+        <v>0.1399946327936309</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -17920,7 +17908,7 @@
         <v>1</v>
       </c>
       <c r="K147" t="n">
-        <v>24.0832811521603</v>
+        <v>24</v>
       </c>
       <c r="L147" t="n">
         <v>0.15</v>
@@ -18143,7 +18131,7 @@
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="n">
-        <v>1.840493827160494</v>
+        <v>0.4175278809367771</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -18262,7 +18250,7 @@
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04450409720259961</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -18381,7 +18369,7 @@
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="n">
-        <v>0.9095842696629214</v>
+        <v>0.4390075921908894</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -18619,7 +18607,7 @@
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="n">
-        <v>1.377016129032258</v>
+        <v>0.6419172932330827</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -18976,7 +18964,7 @@
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>0.01923076923076923</v>
+        <v>0.01538461538461539</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -19214,7 +19202,7 @@
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
-        <v>1.282101167315175</v>
+        <v>0.3655695266272189</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -19333,7 +19321,7 @@
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>0.3</v>
+        <v>0.1917747278936075</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -19452,7 +19440,7 @@
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
-        <v>1.399333333333333</v>
+        <v>0.5879551820728292</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -19571,7 +19559,7 @@
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>2.077169811320755</v>
+        <v>0.6456891495601174</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -19690,7 +19678,7 @@
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>0.4690026954177898</v>
+        <v>0.4317617866004963</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -19809,7 +19797,7 @@
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>0.3305785123966942</v>
+        <v>0.1809954751131222</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -19928,7 +19916,7 @@
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
-        <v>1.283636363636364</v>
+        <v>0.3519441674975075</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -20285,7 +20273,7 @@
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="n">
-        <v>0.116</v>
+        <v>0.04145818441744103</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -20404,7 +20392,7 @@
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -20523,7 +20511,7 @@
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -20642,7 +20630,7 @@
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -20880,7 +20868,7 @@
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
-        <v>2.833127659574468</v>
+        <v>0.4334537760416666</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -20999,7 +20987,7 @@
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="n">
-        <v>0.775</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -21118,7 +21106,7 @@
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="n">
-        <v>0.9130681818181817</v>
+        <v>0.3529928610653487</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -21133,7 +21121,7 @@
         <v>1</v>
       </c>
       <c r="K174" t="n">
-        <v>15.30148270181219</v>
+        <v>15</v>
       </c>
       <c r="L174" t="n">
         <v>0.15</v>
@@ -21237,7 +21225,7 @@
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
-        <v>1.381085714285714</v>
+        <v>0.3738437741686002</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -21356,7 +21344,7 @@
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
-        <v>1.42454754601227</v>
+        <v>0.4132614015572859</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -21475,7 +21463,7 @@
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -21832,7 +21820,7 @@
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>0.1480645161290323</v>
+        <v>0.1136138613861386</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -21847,7 +21835,7 @@
         <v>1</v>
       </c>
       <c r="K180" t="n">
-        <v>13.48514851485148</v>
+        <v>13</v>
       </c>
       <c r="L180" t="n">
         <v>0.15</v>
@@ -21951,7 +21939,7 @@
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
-        <v>0.2522727272727273</v>
+        <v>0.212527352297593</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -21966,7 +21954,7 @@
         <v>1</v>
       </c>
       <c r="K181" t="n">
-        <v>3.962800875273523</v>
+        <v>4</v>
       </c>
       <c r="L181" t="n">
         <v>0.15</v>
@@ -22308,7 +22296,7 @@
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="n">
-        <v>2.823847566574839</v>
+        <v>0.3664996156436033</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -22665,7 +22653,7 @@
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="n">
-        <v>0.7956834532374101</v>
+        <v>0.3990378833433554</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -22784,7 +22772,7 @@
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="n">
-        <v>1.057796529862155</v>
+        <v>0.2218699842494913</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -22796,10 +22784,10 @@
         <v>0.0258446775450622</v>
       </c>
       <c r="J188" t="n">
-        <v>0.3535523603975673</v>
+        <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>7.424599568348913</v>
+        <v>7</v>
       </c>
       <c r="L188" t="n">
         <v>0.15</v>
@@ -22903,7 +22891,7 @@
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="n">
-        <v>0.7400611620795107</v>
+        <v>0.4002205071664829</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -23022,7 +23010,7 @@
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="n">
-        <v>2.535911602209945</v>
+        <v>0.4803767660910518</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -23141,7 +23129,7 @@
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="n">
-        <v>0.7170294494238156</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -23260,7 +23248,7 @@
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="n">
-        <v>1.96415770609319</v>
+        <v>0.4</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -23498,7 +23486,7 @@
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="n">
-        <v>0.6875151515151515</v>
+        <v>0.2988377361671637</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -23629,7 +23617,7 @@
         <v>0.04</v>
       </c>
       <c r="J195" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K195" t="n">
         <v>27</v>
@@ -23855,7 +23843,7 @@
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="n">
-        <v>0.6312491535370862</v>
+        <v>0.2546308773718906</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -23867,7 +23855,7 @@
         <v>0.07544742688567578</v>
       </c>
       <c r="J197" t="n">
-        <v>2.024328950722948</v>
+        <v>2</v>
       </c>
       <c r="K197" t="n">
         <v>27</v>
@@ -23974,7 +23962,7 @@
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="n">
-        <v>2.989317507418397</v>
+        <v>0.6526724975704566</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -23989,7 +23977,7 @@
         <v>7</v>
       </c>
       <c r="K198" t="n">
-        <v>39.68189180434079</v>
+        <v>40</v>
       </c>
       <c r="L198" t="n">
         <v>0.15</v>
@@ -24093,7 +24081,7 @@
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="n">
-        <v>0.6</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -24108,7 +24096,7 @@
         <v>1</v>
       </c>
       <c r="K199" t="n">
-        <v>13.56209150326797</v>
+        <v>14</v>
       </c>
       <c r="L199" t="n">
         <v>0.15</v>
@@ -24212,7 +24200,7 @@
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="n">
-        <v>0.8632520325203252</v>
+        <v>0.2902679059595407</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -24331,7 +24319,7 @@
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="n">
-        <v>1.090909090909091</v>
+        <v>0.5504587155963303</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -24343,7 +24331,7 @@
         <v>0.005045871559633028</v>
       </c>
       <c r="J201" t="n">
-        <v>0.5045871559633027</v>
+        <v>1</v>
       </c>
       <c r="K201" t="n">
         <v>26</v>
@@ -24569,7 +24557,7 @@
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="n">
-        <v>4.99672131147541</v>
+        <v>0.7377022993657891</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -24581,10 +24569,10 @@
         <v>0.04634190371726445</v>
       </c>
       <c r="J203" t="n">
-        <v>1.540097798800895</v>
+        <v>2</v>
       </c>
       <c r="K203" t="n">
-        <v>31.97966768544452</v>
+        <v>32</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>
@@ -24688,7 +24676,7 @@
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="n">
-        <v>1.311475409836065</v>
+        <v>0.6557377049180327</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -24700,7 +24688,7 @@
         <v>0.0385</v>
       </c>
       <c r="J204" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K204" t="n">
         <v>27</v>
@@ -24807,7 +24795,7 @@
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="n">
-        <v>0.5171428571428572</v>
+        <v>0.4022222222222223</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -24926,7 +24914,7 @@
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="n">
-        <v>2.308857142857143</v>
+        <v>0.4</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -25045,7 +25033,7 @@
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="n">
-        <v>0.698666925477895</v>
+        <v>0.4</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -25164,7 +25152,7 @@
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="n">
-        <v>0.08928571428571429</v>
+        <v>0.03311258278145696</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -25402,7 +25390,7 @@
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="n">
-        <v>0.5674157303370787</v>
+        <v>0.1630785791173305</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -25640,7 +25628,7 @@
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="n">
-        <v>0.7859306596847524</v>
+        <v>0.51928382223574</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -25997,7 +25985,7 @@
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="n">
-        <v>0.6283798821919208</v>
+        <v>0.4737889219230008</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -26012,7 +26000,7 @@
         <v>1</v>
       </c>
       <c r="K215" t="n">
-        <v>19.46015132963318</v>
+        <v>19</v>
       </c>
       <c r="L215" t="n">
         <v>0</v>
@@ -26235,7 +26223,7 @@
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="n">
-        <v>0.5700019718778602</v>
+        <v>0.1920539842731593</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -26247,7 +26235,7 @@
         <v>0.05614809624121472</v>
       </c>
       <c r="J217" t="n">
-        <v>0.9353265211723645</v>
+        <v>1</v>
       </c>
       <c r="K217" t="n">
         <v>27</v>
@@ -26354,7 +26342,7 @@
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="n">
-        <v>0.3587452167292876</v>
+        <v>0.1931788814193691</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -26366,7 +26354,7 @@
         <v>0.09256926603565364</v>
       </c>
       <c r="J218" t="n">
-        <v>0.6222987310251633</v>
+        <v>1</v>
       </c>
       <c r="K218" t="n">
         <v>27</v>
@@ -26830,7 +26818,7 @@
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="n">
-        <v>0.1439642656688494</v>
+        <v>0.1237538397208061</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -26842,7 +26830,7 @@
         <v>0.09730596089460676</v>
       </c>
       <c r="J222" t="n">
-        <v>1.859614982550379</v>
+        <v>2</v>
       </c>
       <c r="K222" t="n">
         <v>27</v>
@@ -27187,7 +27175,7 @@
       <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="n">
-        <v>4.994205005817635</v>
+        <v>0.8439999999999999</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -27199,7 +27187,7 @@
         <v>0.01155824887362251</v>
       </c>
       <c r="J225" t="n">
-        <v>2.365942124169074</v>
+        <v>2</v>
       </c>
       <c r="K225" t="n">
         <v>18</v>
@@ -27306,7 +27294,7 @@
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="n">
-        <v>9.647619047619047</v>
+        <v>0.4</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -27425,7 +27413,7 @@
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="n">
-        <v>5.743376623376624</v>
+        <v>0.4</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -27544,7 +27532,7 @@
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="n">
-        <v>14.52050632911392</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -27663,7 +27651,7 @@
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="n">
-        <v>1.843864457456085</v>
+        <v>0.2</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -27782,7 +27770,7 @@
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="n">
-        <v>4.175892617449664</v>
+        <v>0.2</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -27901,7 +27889,7 @@
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="n">
-        <v>0.6174112256586484</v>
+        <v>0.5</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -28020,7 +28008,7 @@
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="n">
-        <v>2.480165289256199</v>
+        <v>0.4</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -28139,7 +28127,7 @@
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>2.196666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -28258,7 +28246,7 @@
       <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>1.17479674796748</v>
+        <v>0.4873524451939292</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -28496,7 +28484,7 @@
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>1.10126582278481</v>
+        <v>0.2230769230769231</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -28734,7 +28722,7 @@
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>0.8228571428571428</v>
+        <v>0.4114285714285714</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -28853,7 +28841,7 @@
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>0.09375</v>
+        <v>0.07894736842105263</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -28868,7 +28856,7 @@
         <v>1</v>
       </c>
       <c r="K239" t="n">
-        <v>14.26315789473684</v>
+        <v>14</v>
       </c>
       <c r="L239" t="n">
         <v>0.15</v>

--- a/tests/antares/resources/expected_output_files/thermal/specific_2035.xlsx
+++ b/tests/antares/resources/expected_output_files/thermal/specific_2035.xlsx
@@ -7696,7 +7696,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.5990410458839226</v>
+        <v>0.5</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -7812,7 +7812,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.946790380609733</v>
+        <v>0.5</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -8392,7 +8392,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>7.366482504604051</v>
+        <v>0.4</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.3168578522602152</v>
+        <v>0.3160847769871296</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -8972,7 +8972,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1.242242903755823</v>
+        <v>0.5</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.6763542288382415</v>
+        <v>0.5</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -10016,7 +10016,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1.142857142857143</v>
+        <v>0.4</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -10132,7 +10132,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.4</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -24980,7 +24980,7 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>0.51928382223574</v>
+        <v>0.3602285236087067</v>
       </c>
       <c r="D212" t="n">
         <v>0</v>
@@ -25096,7 +25096,7 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>0.1775110245694023</v>
+        <v>0.1373</v>
       </c>
       <c r="D213" t="n">
         <v>0</v>
@@ -25792,7 +25792,7 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>0.09037037037037036</v>
+        <v>0.0183</v>
       </c>
       <c r="D219" t="n">
         <v>0</v>
@@ -25908,7 +25908,7 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>0.02294670846394984</v>
+        <v>0.0183</v>
       </c>
       <c r="D220" t="n">
         <v>0</v>
@@ -26140,7 +26140,7 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>0.1237538397208061</v>
+        <v>0.0751652792743531</v>
       </c>
       <c r="D222" t="n">
         <v>0</v>
@@ -26256,7 +26256,7 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>0.4580701754385966</v>
+        <v>0.2611</v>
       </c>
       <c r="D223" t="n">
         <v>0</v>

--- a/tests/antares/resources/expected_output_files/thermal/specific_2035.xlsx
+++ b/tests/antares/resources/expected_output_files/thermal/specific_2035.xlsx
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.06057164489873178</v>
+        <v>0.5</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.1921209931257863</v>
+        <v>0.3412979595035241</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.2364559819413093</v>
+        <v>0.3594808126410835</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -5956,7 +5956,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.2302244854524251</v>
+        <v>0.2314364543939111</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.1006806239789063</v>
+        <v>0.1180273889649343</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.1148377688662049</v>
+        <v>0.2812613926358002</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -9204,7 +9204,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -11060,7 +11060,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -11988,7 +11988,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -12916,7 +12916,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0.01677926423000926</v>
+        <v>0.2076438870381153</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -14540,7 +14540,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -15120,7 +15120,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0.2946928496798564</v>
+        <v>0.3108741661531867</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -15236,7 +15236,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>0.175448275862069</v>
+        <v>0.1768275862068966</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -15584,7 +15584,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0.1093650793650794</v>
+        <v>0.3911111111111111</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -15700,7 +15700,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>0.1660280970625798</v>
+        <v>0.1803320561941252</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -15816,7 +15816,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>0.1314516129032258</v>
+        <v>0.2524193548387097</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -16280,7 +16280,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>0.2291666666666667</v>
+        <v>0.3125</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -16512,7 +16512,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>0.3365511899480516</v>
+        <v>0.3493827845118327</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -16744,7 +16744,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>0.1529078014184397</v>
+        <v>0.4699290780141844</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0.342394520986545</v>
+        <v>0.3459001173790526</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -16976,7 +16976,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0.2830948191816993</v>
+        <v>0.2883641244925506</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -17092,7 +17092,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0.2984149855907781</v>
+        <v>0.3312680115273775</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -17440,7 +17440,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>0.1399946327936309</v>
+        <v>0.1735396726004115</v>
       </c>
       <c r="D147" t="n">
         <v>0</v>
@@ -17788,7 +17788,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>0.04450409720259961</v>
+        <v>0.2115004238485448</v>
       </c>
       <c r="D150" t="n">
         <v>0</v>
@@ -18136,7 +18136,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>0.6419172932330827</v>
+        <v>0.6644736842105263</v>
       </c>
       <c r="D153" t="n">
         <v>0</v>
@@ -18484,7 +18484,7 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>0.01538461538461539</v>
+        <v>0.4153846153846154</v>
       </c>
       <c r="D156" t="n">
         <v>0</v>
@@ -18832,7 +18832,7 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>0.1917747278936075</v>
+        <v>0.2639249092978692</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>0.1809954751131222</v>
+        <v>0.2904977375565611</v>
       </c>
       <c r="D163" t="n">
         <v>0</v>
@@ -21848,7 +21848,7 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>0</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="D185" t="n">
         <v>0</v>
@@ -21964,7 +21964,7 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D186" t="n">
         <v>0</v>
@@ -22196,7 +22196,7 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>0.2218699842494913</v>
+        <v>0.4804490400904645</v>
       </c>
       <c r="D188" t="n">
         <v>0</v>
@@ -22776,7 +22776,7 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D193" t="n">
         <v>0</v>
@@ -22892,7 +22892,7 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>0.2988377361671637</v>
+        <v>0.3003171726325329</v>
       </c>
       <c r="D194" t="n">
         <v>0</v>
@@ -25212,7 +25212,7 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D214" t="n">
         <v>0</v>
@@ -26720,7 +26720,7 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D227" t="n">
         <v>0</v>
@@ -28112,7 +28112,7 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>0.07894736842105263</v>
+        <v>0.5</v>
       </c>
       <c r="D239" t="n">
         <v>0</v>

--- a/tests/antares/resources/expected_output_files/thermal/specific_2035.xlsx
+++ b/tests/antares/resources/expected_output_files/thermal/specific_2035.xlsx
@@ -26720,7 +26720,7 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D227" t="n">
         <v>0</v>

--- a/tests/antares/resources/expected_output_files/thermal/specific_2035.xlsx
+++ b/tests/antares/resources/expected_output_files/thermal/specific_2035.xlsx
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.2</v>
+        <v>0.133</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -7812,7 +7812,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.5</v>
+        <v>0.265</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -8392,7 +8392,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.4</v>
+        <v>0.265</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -8972,7 +8972,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.5</v>
+        <v>0.265</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.5</v>
+        <v>0.272</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -9204,7 +9204,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -9320,7 +9320,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.5</v>
+        <v>0.238</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -11060,7 +11060,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0.2</v>
+        <v>0.146</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.6599143129165345</v>
+        <v>0.653</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
@@ -18368,7 +18368,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.3</v>
       </c>
       <c r="D155" t="n">
         <v>0</v>
@@ -21848,7 +21848,7 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>0.4000000000000001</v>
+        <v>0.272</v>
       </c>
       <c r="D185" t="n">
         <v>0</v>
@@ -22776,7 +22776,7 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>0.5</v>
+        <v>0.304</v>
       </c>
       <c r="D193" t="n">
         <v>0</v>
@@ -24864,7 +24864,7 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>0.1667</v>
+        <v>0</v>
       </c>
       <c r="D211" t="n">
         <v>0</v>
@@ -24980,7 +24980,7 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>0.3602285236087067</v>
+        <v>0</v>
       </c>
       <c r="D212" t="n">
         <v>0</v>
@@ -25096,7 +25096,7 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>0.1373</v>
+        <v>0</v>
       </c>
       <c r="D213" t="n">
         <v>0</v>
@@ -25212,7 +25212,7 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>0.5</v>
+        <v>0.373</v>
       </c>
       <c r="D214" t="n">
         <v>0</v>
@@ -25444,7 +25444,7 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D216" t="n">
         <v>0</v>
@@ -25560,7 +25560,7 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>0.1920539842731593</v>
+        <v>0.174</v>
       </c>
       <c r="D217" t="n">
         <v>0</v>

--- a/tests/antares/resources/expected_output_files/thermal/specific_2035.xlsx
+++ b/tests/antares/resources/expected_output_files/thermal/specific_2035.xlsx
@@ -24864,7 +24864,7 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>0</v>
+        <v>0.1667</v>
       </c>
       <c r="D211" t="n">
         <v>0</v>
@@ -24980,7 +24980,7 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>0</v>
+        <v>0.3602285236087067</v>
       </c>
       <c r="D212" t="n">
         <v>0</v>
@@ -25096,7 +25096,7 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>0</v>
+        <v>0.1373</v>
       </c>
       <c r="D213" t="n">
         <v>0</v>
@@ -25444,7 +25444,7 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D216" t="n">
         <v>0</v>
